--- a/naver-place-crawler/results_health/노원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/노원_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -6281,35 +6281,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경영컨설팅</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>경영컨설턴트안젤라</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>MVGym</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>mvgym@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1342-4856</t>
+          <t>0507-1481-0042</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 월계로 372 0</t>
+          <t>서울특별시 노원구 동일로 1323 B2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_IuVVb</t>
+          <t>https://smartstore.naver.com/mvgym</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6330,22 +6334,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>18204</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>838</v>
       </c>
       <c r="R63" t="n">
-        <v>14</v>
+        <v>19042</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,12 +6358,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1996601981</t>
+          <t>1962632260</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996601981</t>
+          <t>https://m.place.naver.com/place/1962632260</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6371,43 +6375,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>쥬비스 노원점</t>
+          <t>팔로우짐 중계점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>juvisnw1@naver.com</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>foodsales@juvis.co.kr</t>
-        </is>
-      </c>
+          <t>followgym3_@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02-935-0442</t>
+          <t>0507-1396-7040</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노해로 452 노빌리안골드 빌딩 2층</t>
+          <t>서울특별시 노원구 덕릉로 459-37 상가동 지하1호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://vo.la/CGQFb</t>
+          <t>https://blog.naver.com/followgym3_</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6428,7 +6428,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="Q64" t="n">
-        <v>4513</v>
+        <v>344</v>
       </c>
       <c r="R64" t="n">
-        <v>4860</v>
+        <v>543</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,12 +6452,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>12904175</t>
+          <t>2074166663</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12904175</t>
+          <t>https://m.place.naver.com/place/2074166663</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6469,39 +6469,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>목욕,찜질</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>스파렉스 공릉점</t>
+          <t>에이블짐 노원본점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jyspafit3@naver.com</t>
+          <t>ablegym2@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02-948-9999</t>
+          <t>0507-1342-0491</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로46길 23 한보아파트상가 지하1층</t>
+          <t>서울특별시 노원구 상계로 77 다나프라자 B1F</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155225351</t>
+          <t>https://blog.naver.com/ablegym2/224059212843</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6531,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>144</v>
+        <v>3267</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>2621</v>
       </c>
       <c r="R65" t="n">
-        <v>149</v>
+        <v>5888</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6546,12 +6546,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>31114768</t>
+          <t>37471634</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31114768</t>
+          <t>https://m.place.naver.com/place/37471634</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6563,44 +6563,44 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>문화센터</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>삼육대학교 체육 문화 센터</t>
+          <t>아이원휘트니스클럽</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>waterpole2@naver.com</t>
+          <t>la-lune@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1419-3715</t>
+          <t>070-8111-7941</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 화랑로 815</t>
+          <t>서울특별시 노원구 섬밭로 139 공릉풍림아파트</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.syu.ac.kr/sportscenter</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6621,17 +6621,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1521716419</t>
+          <t>37495816</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1521716419</t>
+          <t>https://m.place.naver.com/place/37495816</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6657,39 +6657,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엑시온트레이닝센터 월계점</t>
+          <t>커브스 중계은행클럽</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>flamingbean@naver.com</t>
+          <t>curves8080@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1311-9630</t>
+          <t>02-933-8080</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 초안산로2라길 11 지하 1층</t>
+          <t>서울특별시 노원구 중계로 225 청구상가 3층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/xion_korea/</t>
+          <t>http://m.curveskorea.co.kr/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6719,13 +6719,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="R67" t="n">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6734,12 +6734,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2010458342</t>
+          <t>20989974</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010458342</t>
+          <t>https://m.place.naver.com/place/20989974</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6751,34 +6751,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MNF그룹.PT상계점</t>
+          <t>커브스 마들클럽</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>patience1011@naver.com</t>
+          <t>hockey2007@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1439-1324</t>
+          <t>0507-1488-5030</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로12길 65 상가동 201호</t>
+          <t>서울특별시 노원구 동일로 1551 삼전빌딩</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/patience1011</t>
+          <t>https://blog.naver.com/hockey2007</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="Q68" t="n">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="R68" t="n">
-        <v>117</v>
+        <v>358</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6828,12 +6828,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1830791616</t>
+          <t>13456699</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830791616</t>
+          <t>https://m.place.naver.com/place/13456699</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6845,34 +6845,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>에이블짐 중계점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>ablegym3_junggye@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>0507-1355-0490</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울특별시 노원구 동일로204가길 34 씨앤미 복합빌딩 지하1층 에이블짐휘트니스</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline-pt</t>
+          <t>https://blog.naver.com/ablegym3_junggye/224236181530</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>130</v>
+        <v>1957</v>
       </c>
       <c r="Q69" t="n">
-        <v>586</v>
+        <v>1172</v>
       </c>
       <c r="R69" t="n">
-        <v>716</v>
+        <v>3129</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6922,12 +6922,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>1552031422</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/1552031422</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6939,34 +6939,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에스핏 퍼스널트레이닝 노원점</t>
+          <t>레몬핏 중계점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1983sim@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1380-5118</t>
+          <t>02-989-1119</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로34길 112 지하1층 일부 B02호</t>
+          <t>서울특별시 노원구 덕릉로73길 18 태인빌딩 3층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/1983sim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6976,20 +6976,24 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41f8f</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -6997,17 +7001,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="Q70" t="n">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="R70" t="n">
-        <v>439</v>
+        <v>224</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7016,12 +7020,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1698163500</t>
+          <t>33623419</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698163500</t>
+          <t>https://m.place.naver.com/place/33623419</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7033,57 +7037,61 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>핏피티</t>
+          <t>발리짐 상계역점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>fitpt_official@naver.com</t>
+          <t>baligymnowon@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1369-0837</t>
+          <t>0507-1405-6733</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로239가길 22 4층 (상계동, 한올빌딩)</t>
+          <t>서울특별시 노원구 덕릉로 699 우암에이스타워 3층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitpt_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xqyx</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7095,13 +7103,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="Q71" t="n">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="R71" t="n">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,12 +7118,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1936659906</t>
+          <t>11493661</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936659906</t>
+          <t>https://m.place.naver.com/place/11493661</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7127,34 +7135,34 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>070-5250-9123</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 하계동</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7164,12 +7172,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7185,17 +7193,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7204,12 +7212,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1608265211</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1608265211</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7221,39 +7229,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>드랍더핏피티스튜디오</t>
+          <t>알지티짐 노원역점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dropthefit_pt@naver.com</t>
+          <t>chans_gym@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1395-8606</t>
+          <t>0507-1383-9081</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1352 6층 드랍더핏피티스튜디오</t>
+          <t>서울특별시 노원구 노해로85길 14 5층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dropthefit_pt</t>
+          <t>http://pf.kakao.com/_xmVvxoxj</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7263,7 +7271,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7283,13 +7291,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="Q73" t="n">
-        <v>109</v>
+        <v>749</v>
       </c>
       <c r="R73" t="n">
-        <v>260</v>
+        <v>865</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,12 +7306,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1725462537</t>
+          <t>1820809502</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725462537</t>
+          <t>https://m.place.naver.com/place/1820809502</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7315,34 +7323,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>스포애니 공릉동점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>spoany_57@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>02-949-9618</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 동일로192길 74 B1,2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeong_seok_moon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7352,20 +7360,24 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j3u</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>X</t>
@@ -7377,13 +7389,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>36</v>
+        <v>959</v>
       </c>
       <c r="Q74" t="n">
-        <v>74</v>
+        <v>1993</v>
       </c>
       <c r="R74" t="n">
-        <v>110</v>
+        <v>2952</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,12 +7404,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1077112071</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1077112071</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7409,25 +7421,29 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>바디짐</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>씨앤지체육관</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>cyber_gongju@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>02-935-3375</t>
+          <t>02-934-6734</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 193-25 벽산빌딩 4층</t>
+          <t>서울특별시 노원구 한글비석로 245</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7467,13 +7483,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7482,12 +7498,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1235879217</t>
+          <t>18064033</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235879217</t>
+          <t>https://m.place.naver.com/place/18064033</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7499,34 +7515,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>리핏트레이닝센터 PT 노원역점</t>
+          <t>두더짐</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>leefitnowon@naver.com</t>
+          <t>allinsighter@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1442-5622</t>
+          <t>0507-1442-0994</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 76 B1층</t>
+          <t>서울특별시 노원구 상계로9가길 59 지층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leefitnowon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7536,12 +7552,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7557,17 +7573,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>253</v>
+        <v>61</v>
       </c>
       <c r="Q76" t="n">
-        <v>317</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>570</v>
+        <v>71</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7576,12 +7592,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1399680010</t>
+          <t>1141609720</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399680010</t>
+          <t>https://m.place.naver.com/place/1141609720</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7593,44 +7609,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>빌리핏 PT&amp;PILA 스튜디오</t>
+          <t>뷰티짐 노원역점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>beliefit@naver.com</t>
+          <t>beautygym0717@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1313-0107</t>
+          <t>0507-1368-0719</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로 105 201호(공릉동, 장원빌딩)</t>
+          <t>서울특별시 노원구 노해로 517 2층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_UrUxgb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7640,13 +7656,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bgkg</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7655,13 +7675,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>278</v>
+        <v>1681</v>
       </c>
       <c r="Q77" t="n">
-        <v>259</v>
+        <v>2448</v>
       </c>
       <c r="R77" t="n">
-        <v>537</v>
+        <v>4129</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7670,12 +7690,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1104811643</t>
+          <t>1573522000</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1104811643</t>
+          <t>https://m.place.naver.com/place/1573522000</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7687,44 +7707,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>트라이스피닝 노원역점</t>
+          <t>굿모닝헬스타운</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>tryspinning@naver.com</t>
+          <t>chlgmlrhkd123@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1356-3794</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 13 지하1층</t>
+          <t>서울특별시 노원구 중계로12가길 29</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://litt.ly/page_tryspinning</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7745,17 +7761,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>462</v>
+        <v>2</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7764,12 +7780,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>2084641911</t>
+          <t>20888465</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084641911</t>
+          <t>https://m.place.naver.com/place/20888465</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7781,34 +7797,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>일상의운동 PT 노원역점</t>
+          <t>블루짐 노원점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>dailyworkout01@naver.com</t>
+          <t>blugym1@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1375-7281</t>
+          <t>0507-1410-9999</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 70 4층</t>
+          <t>서울특별시 노원구 동일로218길 41 지하1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyworkout01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7818,23 +7834,27 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy8t6p4</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7843,13 +7863,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="Q79" t="n">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="R79" t="n">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7858,12 +7878,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1567478488</t>
+          <t>2064049169</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567478488</t>
+          <t>https://m.place.naver.com/place/2064049169</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7875,34 +7895,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공릉 라이크짐 PT</t>
+          <t>위고짐</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>likegym88@naver.com</t>
+          <t>zhsclahs@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1301-6597</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 동일로 1639-6 6층 601호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7912,20 +7928,24 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wypo57v</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
           <t>X</t>
@@ -7933,17 +7953,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>1717</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2110</v>
+        <v>0</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7952,12 +7972,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1754784084</t>
+          <t>2011065741</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754784084</t>
+          <t>https://m.place.naver.com/place/2011065741</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7969,40 +7989,44 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>김정민 퍼스널트레이닝 스튜디오</t>
+          <t>에이치짐 공릉점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dropzone96@naver.com</t>
+          <t>h-gym@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1358-8248</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로3길 58 노원 현대아파트 상가 지하2호</t>
+          <t>서울특별시 노원구 공릉로46길 18 3층 302호~308호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dropzone96</t>
+          <t>https://booking.naver.com/booking/5/bizes/815316</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8023,17 +8047,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>5</v>
+        <v>1115</v>
       </c>
       <c r="Q81" t="n">
-        <v>16796</v>
+        <v>1987</v>
       </c>
       <c r="R81" t="n">
-        <v>16801</v>
+        <v>3102</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8042,12 +8066,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>21349016</t>
+          <t>1377484075</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21349016</t>
+          <t>https://m.place.naver.com/place/1377484075</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8059,34 +8083,30 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>데이포짐 노원역점</t>
+          <t>뉴크로핏</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>trainersj@naver.com</t>
+          <t>la-lune@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>0507-1382-9041</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1379 302호 데이포짐</t>
+          <t>서울특별시 노원구 동일로192길 63</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trainersj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8096,12 +8116,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8117,17 +8137,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>336</v>
+        <v>10</v>
       </c>
       <c r="R82" t="n">
-        <v>429</v>
+        <v>10</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8136,12 +8156,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1529006296</t>
+          <t>1849862084</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529006296</t>
+          <t>https://m.place.naver.com/place/1849862084</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8153,39 +8173,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>무드짐</t>
+          <t>피트니스 서울 상계점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mood_gym@naver.com</t>
+          <t>fitness_seoul@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1375-3047</t>
+          <t>0507-1454-7669</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로49길 63 지하1층</t>
+          <t>서울특별시 노원구 덕릉로 688 우리빌딩 3층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mood_gym_?igsh=bDhhaDd5NHZlc2Uz</t>
+          <t>https://talk.naver.com/profile/w5vg3y</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8200,10 +8220,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
           <t>X</t>
@@ -8215,13 +8239,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>25</v>
+        <v>630</v>
       </c>
       <c r="Q83" t="n">
-        <v>15</v>
+        <v>394</v>
       </c>
       <c r="R83" t="n">
-        <v>40</v>
+        <v>1024</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8230,12 +8254,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1090358176</t>
+          <t>1860425511</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090358176</t>
+          <t>https://m.place.naver.com/place/1860425511</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8247,34 +8271,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>핏피티 상계역점</t>
+          <t>점핑피트니스 노원점</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>fitpt_official@naver.com</t>
+          <t>tenyears0624@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1497-7447</t>
+          <t>0507-1306-6646</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 덕릉로83길 9-8 3층</t>
+          <t>서울특별시 노원구 동일로239길 10 2층 203호</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitpt_official2</t>
+          <t>https://www.instagram.com/jumping_yurin_</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8300,7 +8324,7 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8309,13 +8333,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="Q84" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>221</v>
+        <v>11</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8324,12 +8348,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1513557300</t>
+          <t>2059861597</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513557300</t>
+          <t>https://m.place.naver.com/place/2059861597</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8341,34 +8365,34 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>헬로헤일리</t>
+          <t>위너블 헬스피티 앤 필라</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>hansj7917@naver.com</t>
+          <t>winnable23@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1314-7917</t>
+          <t>0507-1484-1369</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 섬밭로 196 상가동 205호</t>
+          <t>서울특별시 노원구 동일로192길 83 3층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://youtube.com/@hello._hailey</t>
+          <t>https://open.kakao.com/o/scDFWR2h</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8394,7 +8418,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8403,13 +8427,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>28</v>
+        <v>137</v>
       </c>
       <c r="Q85" t="n">
-        <v>36</v>
+        <v>570</v>
       </c>
       <c r="R85" t="n">
-        <v>64</v>
+        <v>707</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8418,12 +8442,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1125055731</t>
+          <t>1929122000</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125055731</t>
+          <t>https://m.place.naver.com/place/1929122000</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8435,39 +8459,43 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>조아짐</t>
+          <t>휘트니스인X필라테스인 마들점</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mutac@naver.com</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>fitness_in@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>inpakorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1446-0427</t>
+          <t>0507-1355-7207</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 덕릉로 738 2층 조아짐 (정진145빌딩)</t>
+          <t>서울특별시 노원구 수락산로 190 지하1층 비101호</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jamie_buendia</t>
+          <t>https://www.inpakorea.com/</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8477,7 +8505,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8488,7 +8516,7 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8497,13 +8525,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>28</v>
+        <v>2442</v>
       </c>
       <c r="Q86" t="n">
-        <v>46</v>
+        <v>774</v>
       </c>
       <c r="R86" t="n">
-        <v>74</v>
+        <v>3216</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8512,12 +8540,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1748054991</t>
+          <t>1857719873</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748054991</t>
+          <t>https://m.place.naver.com/place/1857719873</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8529,34 +8557,34 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>라온 짐</t>
+          <t>프리원핏 노원점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>raon_gym19@naver.com</t>
+          <t>roseto90@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02-935-1114</t>
+          <t>0507-1333-3857</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 덕릉로73길 15 2층 라온짐</t>
+          <t>서울특별시 노원구 상계로9가길 17 지하1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/raon_gym19</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8566,7 +8594,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8587,17 +8615,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8606,12 +8634,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1951994273</t>
+          <t>2004620826</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951994273</t>
+          <t>https://m.place.naver.com/place/2004620826</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8623,30 +8651,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>피트니스 고집</t>
+          <t>SN휘트니스 중계점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sangdopark1@naver.com</t>
+          <t>nopain_nogain@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1303-3875</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로7길 13 B1층</t>
+          <t>서울특별시 노원구 중계로 202 신아프라자 지하1층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nopain_nogain</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8656,12 +8688,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8677,17 +8709,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="Q88" t="n">
-        <v>528</v>
+        <v>440</v>
       </c>
       <c r="R88" t="n">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8696,12 +8728,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>34069567</t>
+          <t>1310395697</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34069567</t>
+          <t>https://m.place.naver.com/place/1310395697</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8713,34 +8745,34 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>제이지휘트니스</t>
+          <t>써클핏</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>beomgym@naver.com</t>
+          <t>wernono@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>02-975-3397</t>
+          <t>0507-1441-2343</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로16길 15 어린이집 지하 1층</t>
+          <t>서울특별시 노원구 노원로26길 181 지층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beomgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8750,12 +8782,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8775,13 +8807,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8790,12 +8822,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1660850292</t>
+          <t>1897747556</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660850292</t>
+          <t>https://m.place.naver.com/place/1897747556</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8807,29 +8839,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>와이핏 퍼스널트레이닝</t>
+          <t>상계1단지 헬스원</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jeongmo1318@naver.com</t>
+          <t>sunnydue@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>0507-1308-8465</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 325 2층 204호</t>
+          <t>서울특별시 노원구 덕릉로 459-21 124동 앞 지하 헬스1원 휘트니스</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8854,14 +8882,10 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44rfn</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>X</t>
@@ -8873,13 +8897,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="Q90" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R90" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8888,12 +8912,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1378559215</t>
+          <t>11861328</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1378559215</t>
+          <t>https://m.place.naver.com/place/11861328</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8905,34 +8929,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>윤스피티 월계점</t>
+          <t>카인드짐 헬스&amp;PT&amp;스쿼시 24시 수락산역점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>yoons-pt@naver.com</t>
+          <t>kindgym17@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1399-8981</t>
+          <t>0507-1396-5289</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 초안산로2라길 27 2층</t>
+          <t>서울특별시 노원구 동일로 1665 대은빌딩 5, 6, 7층</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/kindgym17</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8942,42 +8966,38 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w437t9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2384</v>
       </c>
       <c r="Q91" t="n">
-        <v>44</v>
+        <v>824</v>
       </c>
       <c r="R91" t="n">
-        <v>44</v>
+        <v>3208</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8986,12 +9006,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1922600514</t>
+          <t>1423020842</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922600514</t>
+          <t>https://m.place.naver.com/place/1423020842</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9003,39 +9023,39 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>바디씨피알 PT센터</t>
+          <t>레몬핏 마들점</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>bodycpr@naver.com</t>
+          <t>jjoseohyun@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1461-0160</t>
+          <t>0507-1436-1347</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 23 3층 바디씨피알</t>
+          <t>서울특별시 노원구 동일로 1596 송헌빌딩3층</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodycpr</t>
+          <t>http://cafe.naver.com/lemonfit2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9045,7 +9065,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9061,17 +9081,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="Q92" t="n">
-        <v>248</v>
+        <v>59</v>
       </c>
       <c r="R92" t="n">
-        <v>377</v>
+        <v>135</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9080,12 +9100,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1431147769</t>
+          <t>36473097</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431147769</t>
+          <t>https://m.place.naver.com/place/36473097</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9097,34 +9117,34 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>찬스스포츠그라운드</t>
+          <t>마이핏 휘트니스</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>chans_sport@naver.com</t>
+          <t>myfit2978@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1359-9819</t>
+          <t>02-974-6631</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 460 B1</t>
+          <t>서울특별시 노원구 공릉로63길 13</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chans_sport</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9134,20 +9154,24 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc222c</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
           <t>X</t>
@@ -9159,13 +9183,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="Q93" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R93" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9174,12 +9198,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2069511927</t>
+          <t>1461015948</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069511927</t>
+          <t>https://m.place.naver.com/place/1461015948</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9196,34 +9220,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>트로이짐다이어트PT 노원역점</t>
+          <t>포미짐 여성전용 헬스 PT 공릉점</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>troygym@naver.com</t>
+          <t>formegym01@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1327-2093</t>
+          <t>0507-1366-4243</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로218길 25 402호</t>
+          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_cfyRn</t>
+          <t>https://blog.naver.com/formegym01</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9233,7 +9257,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9244,7 +9268,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9253,13 +9277,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>10</v>
+        <v>900</v>
       </c>
       <c r="Q94" t="n">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="R94" t="n">
-        <v>177</v>
+        <v>1012</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9268,12 +9292,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1408185308</t>
+          <t>1996116358</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408185308</t>
+          <t>https://m.place.naver.com/place/1996116358</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9285,29 +9309,29 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>해피한휘트니스센터</t>
+          <t>부르스타짐</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>avex04@naver.com</t>
+          <t>burstargym@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>02-933-2100</t>
+          <t>0507-1374-9006</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 중계로 233</t>
+          <t>서울특별시 노원구 화랑로 325 5층</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9332,10 +9356,14 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4kdn6</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
           <t>X</t>
@@ -9343,17 +9371,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="Q95" t="n">
-        <v>13</v>
+        <v>292</v>
       </c>
       <c r="R95" t="n">
-        <v>13</v>
+        <v>575</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9362,12 +9390,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>21090411</t>
+          <t>1268947101</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21090411</t>
+          <t>https://m.place.naver.com/place/1268947101</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -9379,21 +9407,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>유리,창호공사</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>유리특공대</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>바디짐 헬스</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>freeup02@naver.com</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>02-930-4820</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 화랑로47길 38 풍림</t>
+          <t>서울특별시 노원구 한글비석로 444 4층 405,411,412호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9433,13 +9469,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9448,12 +9484,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1618734928</t>
+          <t>1679174889</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618734928</t>
+          <t>https://m.place.naver.com/place/1679174889</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9465,34 +9501,34 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>장소대여</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>아싸짐</t>
+          <t>카인드짐 태릉입구역점</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>spqj44@naver.com</t>
+          <t>kindgym21@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1388-0878</t>
+          <t>0507-1429-2775</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로24길 83 지층 아싸짐</t>
+          <t>서울특별시 노원구 동일로 986 B1 카인드짐 태릉입구역점</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/assa_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9502,7 +9538,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9512,13 +9548,17 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9cv</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9527,13 +9567,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>70</v>
+        <v>845</v>
       </c>
       <c r="Q97" t="n">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="R97" t="n">
-        <v>78</v>
+        <v>1104</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9542,12 +9582,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1725505301</t>
+          <t>1245864008</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725505301</t>
+          <t>https://m.place.naver.com/place/1245864008</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -9559,34 +9599,34 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>체육관</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>파라에스트라 수락주짓수</t>
+          <t>짐 엘리웃 건강증진센터</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>parksy3900@naver.com</t>
+          <t>jg9679@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1307-7531</t>
+          <t>02-972-6020</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1622</t>
+          <t>서울특별시 노원구 섬밭로 229 극동벽산건영A 관리사무소 2층 건강증진센터/ 헬스</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/paraestra_seoul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9596,7 +9636,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9617,17 +9657,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="R98" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9636,12 +9676,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1138836283</t>
+          <t>37417324</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138836283</t>
+          <t>https://m.place.naver.com/place/37417324</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -9653,30 +9693,34 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>유포리아 PT&amp;필라테스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>uphoria_gongneung_2@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>070-4535-6841</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1036 401호</t>
+          <t>서울특별시 노원구 중계동</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uphoria_gongneung_2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9686,12 +9730,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9707,34 +9751,5408 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1039779623</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1039779623</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>인헬서짐 월계역점</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>inhealthergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1402-1156</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 월계로 338 상가 A동 3층, 4층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xavVxlb</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>1353</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1217</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2570</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1619670887</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1619670887</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>카인드짐 헬스&amp;PT 공릉점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>kindgym10@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1369-9222</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1101 B1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4liae</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>1111</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>906</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2017</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1182567643</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1182567643</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>피트니스cc 공릉점</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>dasball5@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02-975-2300</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 공릉로 146 우일빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dosj</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>1017</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>693</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1710</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>34666359</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34666359</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>아폴로휘트니스 하계역점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>apollofit@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1491-6500</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 섬밭로 258 지하 2층</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>815</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>316</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1131</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1064765861</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1064765861</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>헬시온휘트니스 노원역점</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>halcyon0310@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1390-5318</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로5길 26 B1</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhis5e</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>250</v>
+      </c>
+      <c r="R104" t="n">
+        <v>380</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1590788500</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1590788500</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>에이블짐 노원역점</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ablegym9@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1421-9500</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1401 상아빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4wx3d</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>2849</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1478</v>
+      </c>
+      <c r="R105" t="n">
+        <v>4327</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1033654060</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033654060</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>크로스핏라쿤짐</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>helen0216@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>02-931-0809</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로217가길 23 지층 크로스핏 라쿤짐</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>http://www.crossfitkr.com</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vxrq</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>283</v>
+      </c>
+      <c r="R106" t="n">
+        <v>309</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1116921515</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1116921515</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>경영컨설팅</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>경영컨설턴트안젤라</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1342-4856</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 월계로 372 0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_IuVVb</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>13</v>
+      </c>
+      <c r="R107" t="n">
+        <v>14</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1996601981</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1996601981</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>다이어트,비만</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>쥬비스 노원점</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>juvisnw1@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>foodsales@juvis.co.kr</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>02-935-0442</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노해로 452 노빌리안골드 빌딩 2층</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://vo.la/CGQFb</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>347</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>4513</v>
+      </c>
+      <c r="R108" t="n">
+        <v>4860</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>12904175</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12904175</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>목욕,찜질</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>스파렉스 공릉점</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jyspafit3@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>02-948-9999</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 공릉로46길 23 한보아파트상가 지하1층</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1155225351</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>5</v>
+      </c>
+      <c r="R109" t="n">
+        <v>149</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>31114768</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31114768</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>문화센터</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>삼육대학교 체육 문화 센터</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>waterpole2@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1419-3715</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 화랑로 815</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>http://www.syu.ac.kr/sportscenter</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>23</v>
+      </c>
+      <c r="R110" t="n">
+        <v>150</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1521716419</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1521716419</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>엑시온트레이닝센터 월계점</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>flamingbean@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1311-9630</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 초안산로2라길 11 지하 1층</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/xion_korea/</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>12</v>
+      </c>
+      <c r="R111" t="n">
+        <v>22</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2010458342</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2010458342</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MNF그룹.PT상계점</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>patience1011@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1439-1324</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로12길 65 상가동 201호</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/patience1011</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>60</v>
+      </c>
+      <c r="R112" t="n">
+        <v>117</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1830791616</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1830791616</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>바디라인PT</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>bodyline-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1402-8151</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyline-pt</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>586</v>
+      </c>
+      <c r="R113" t="n">
+        <v>716</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1914447631</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914447631</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>에스핏 퍼스널트레이닝 노원점</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1983sim@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1380-5118</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노원로34길 112 지하1층 일부 B02호</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/1983sim</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>246</v>
+      </c>
+      <c r="R114" t="n">
+        <v>439</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>1698163500</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698163500</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>핏피티</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>fitpt_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0507-1369-0837</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로239가길 22 4층 (상계동, 한올빌딩)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitpt_official</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>131</v>
+      </c>
+      <c r="R115" t="n">
+        <v>311</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>1936659906</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1936659906</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>직선 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ziksun001@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1478-9683</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ziksun001</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>388</v>
+      </c>
+      <c r="R116" t="n">
+        <v>486</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>1411508464</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1411508464</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>드랍더핏피티스튜디오</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>dropthefit_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0507-1395-8606</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1352 6층 드랍더핏피티스튜디오</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dropthefit_pt</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>109</v>
+      </c>
+      <c r="R117" t="n">
+        <v>260</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>1725462537</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1725462537</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>베네핏</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>hyeong_seok_moon@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1477-8279</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hyeong_seok_moon</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>74</v>
+      </c>
+      <c r="R118" t="n">
+        <v>110</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1581200562</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1581200562</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>바디짐</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>02-935-3375</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로 193-25 벽산빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>8</v>
+      </c>
+      <c r="R119" t="n">
+        <v>33</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1235879217</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235879217</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>리핏트레이닝센터 PT 노원역점</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>leefitnowon@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0507-1442-5622</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로 76 B1층</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/leefitnowon</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>317</v>
+      </c>
+      <c r="R120" t="n">
+        <v>570</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>1399680010</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399680010</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>빌리핏 PT&amp;PILA 스튜디오</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>beliefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0507-1313-0107</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 공릉로 105 201호(공릉동, 장원빌딩)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_UrUxgb</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>259</v>
+      </c>
+      <c r="R121" t="n">
+        <v>537</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1104811643</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104811643</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>트라이스피닝 노원역점</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>tryspinning@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1356-3794</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로217가길 13 지하1층</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://litt.ly/page_tryspinning</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>394</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>68</v>
+      </c>
+      <c r="R122" t="n">
+        <v>462</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2084641911</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084641911</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>일상의운동 PT 노원역점</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>dailyworkout01@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0507-1375-7281</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로 70 4층</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dailyworkout01</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>174</v>
+      </c>
+      <c r="R123" t="n">
+        <v>399</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>1567478488</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1567478488</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>공릉 라이크짐 PT</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>likegym88@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0507-1301-6597</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/likegym88</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1717</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2110</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>1754784084</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1754784084</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>김정민 퍼스널트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>dropzone96@naver.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로3길 58 노원 현대아파트 상가 지하2호</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dropzone96</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>16796</v>
+      </c>
+      <c r="R125" t="n">
+        <v>16801</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>21349016</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21349016</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>데이포짐 노원역점</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>trainersj@naver.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0507-1382-9041</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1379 302호 데이포짐</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trainersj</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>336</v>
+      </c>
+      <c r="R126" t="n">
+        <v>429</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1529006296</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1529006296</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>무드짐</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>mood_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0507-1375-3047</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로49길 63 지하1층</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mood_gym_?igsh=bDhhaDd5NHZlc2Uz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>15</v>
+      </c>
+      <c r="R127" t="n">
+        <v>40</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1090358176</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090358176</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>핏피티 상계역점</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>fitpt_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0507-1497-7447</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 덕릉로83길 9-8 3층</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitpt_official2</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>96</v>
+      </c>
+      <c r="R128" t="n">
+        <v>221</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>1513557300</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1513557300</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>헬로헤일리</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>hansj7917@naver.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0507-1314-7917</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 섬밭로 196 상가동 205호</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@hello._hailey</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>36</v>
+      </c>
+      <c r="R129" t="n">
+        <v>64</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>1125055731</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125055731</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>조아짐</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>mutac@naver.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1446-0427</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 덕릉로 738 2층 조아짐 (정진145빌딩)</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jamie_buendia</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>46</v>
+      </c>
+      <c r="R130" t="n">
+        <v>74</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>1748054991</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1748054991</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>라온 짐</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>raon_gym19@naver.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>02-935-1114</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 덕릉로73길 15 2층 라온짐</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raon_gym19</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>75</v>
+      </c>
+      <c r="R131" t="n">
+        <v>122</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>1951994273</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951994273</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>피트니스 고집</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>sangdopark1@naver.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로7길 13 B1층</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>528</v>
+      </c>
+      <c r="R132" t="n">
+        <v>529</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>34069567</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34069567</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>제이지휘트니스</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>beomgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>02-975-3397</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노원로16길 15 어린이집 지하 1층</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beomgym</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="n">
         <v>7</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="R133" t="n">
+        <v>8</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>1660850292</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1660850292</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>와이핏 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jeongmo1318@naver.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0507-1308-8465</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로 325 2층 204호</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44rfn</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>9</v>
+      </c>
+      <c r="R134" t="n">
+        <v>68</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>1378559215</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1378559215</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>윤스피티 월계점</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>yoons-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0507-1399-8981</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 초안산로2라길 27 2층</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w437t9</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>44</v>
+      </c>
+      <c r="R135" t="n">
+        <v>44</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>1922600514</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1922600514</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>바디씨피알 PT센터</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>bodycpr@naver.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0507-1461-0160</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로217가길 23 3층 바디씨피알</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodycpr</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>248</v>
+      </c>
+      <c r="R136" t="n">
+        <v>377</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>1431147769</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431147769</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>찬스스포츠그라운드</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>chans_sport@naver.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0507-1359-9819</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로 460 B1</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chans_sport</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>8</v>
+      </c>
+      <c r="R137" t="n">
+        <v>12</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>2069511927</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2069511927</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>트로이짐다이어트PT 노원역점</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>troygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0507-1327-2093</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로218길 25 402호</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_cfyRn</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>167</v>
+      </c>
+      <c r="R138" t="n">
+        <v>177</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>1408185308</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408185308</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>유스짐</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>youthgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0507-1472-7848</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 섬밭로 196 2층 209~211호</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_eKxblG</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>301</v>
+      </c>
+      <c r="R139" t="n">
+        <v>534</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1645686302</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1645686302</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>슬림피티여성전용피트니스 노원점</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>slim-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0507-1317-0226</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 덕릉로 623-10 2층</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>http://www.slim-pt.com</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>160</v>
+      </c>
+      <c r="R140" t="n">
+        <v>164</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1662164509</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1662164509</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>업트레이닝PT 노원역점</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>health-uptoyou@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0507-1323-9688</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로1길 14-11 하이웰빙상가 4층 401호</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/up._.official</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>43</v>
+      </c>
+      <c r="R141" t="n">
+        <v>168</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1226736367</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1226736367</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>다올핏</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>woodnjsrb@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1347-9068</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44jva</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>520</v>
+      </c>
+      <c r="R142" t="n">
+        <v>589</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>1207679430</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1207679430</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MNF퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>patience1011@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0507-1400-7360</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로1길 61 수림빌딩 3층 MNF퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9oki</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>306</v>
+      </c>
+      <c r="R143" t="n">
+        <v>407</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>13528261</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13528261</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>와일드짐</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ringbi92@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0507-1363-8038</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로52길 12 지하1층</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>9</v>
+      </c>
+      <c r="R144" t="n">
+        <v>9</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1741284793</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1741284793</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>남영PT스튜디오 당현천점</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>lifestyle4u@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0507-1386-7855</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노원로26길 63 지하1층</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>5</v>
+      </c>
+      <c r="R145" t="n">
+        <v>5</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2036643272</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036643272</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>원팀월드 피트니스</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>oneteamworld_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>02-971-0998</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 노원로 247 서울온천 지하5층, 6층</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oneteamworld_fitness</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>86</v>
+      </c>
+      <c r="R146" t="n">
+        <v>327</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1314509386</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314509386</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>소운소 Ark Gym</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>joongjae5@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0507-1337-1819</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 중계로14길 37 2층 소운소 Ark Gym</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/joongjae5</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>81</v>
+      </c>
+      <c r="R147" t="n">
+        <v>83</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>1199735123</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1199735123</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>데일리짐 PT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sarere91@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0507-1393-0882</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sarere91</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>236</v>
+      </c>
+      <c r="R148" t="n">
+        <v>283</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1843525848</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843525848</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>수호바디짐</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>wooyoungsu@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>02-933-9688</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로243길 29 2층</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soohogym</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>8</v>
+      </c>
+      <c r="R149" t="n">
+        <v>85</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1626884748</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1626884748</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>버클다운짐 노원점</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jej120506@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1315-3972</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923m</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>3376</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>2753</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6129</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>1930996201</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1930996201</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>실내골프연습장</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>해피한휘트니스센터</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>avex04@naver.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>02-933-2100</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 중계로 233</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>13</v>
+      </c>
+      <c r="R151" t="n">
+        <v>13</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>21090411</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21090411</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>유리,창호공사</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>유리특공대</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 화랑로47길 38 풍림</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>2</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1618734928</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618734928</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>장소대여</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>아싸짐</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>spqj44@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1388-0878</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 한글비석로24길 83 지층 아싸짐</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/assa_gym</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>8</v>
+      </c>
+      <c r="R153" t="n">
+        <v>78</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>1725505301</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1725505301</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>장소대여</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>운동공간 아지트</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>wowm_azit@naver.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0507-1358-6123</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로198길 72 지하1층</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>20</v>
+      </c>
+      <c r="R154" t="n">
+        <v>105</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>1813689551</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1813689551</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>파라에스트라 수락주짓수</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>parksy3900@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0507-1307-7531</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1622</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/paraestra_seoul</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>39</v>
+      </c>
+      <c r="R155" t="n">
+        <v>53</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>1138836283</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1138836283</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>유포리아 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>uphoria_gongneung_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1036 401호</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uphoria_gongneung_2</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q156" t="n">
         <v>22</v>
       </c>
-      <c r="R99" t="n">
+      <c r="R156" t="n">
         <v>29</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
         <is>
           <t>2099980833</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="U156" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2099980833</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="V156" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
